--- a/customer_service_import_template_安全版.xlsx
+++ b/customer_service_import_template_安全版.xlsx
@@ -632,7 +632,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>亲，本店裁剪（也常写剪裁）质量您放心哦。每米面料出厂前都经过验布和质检，裁切边缘平整、不毛边、尺寸精准，按您备注的米数连成整段一起裁。如果您收到的裁剪质量不满意（如毛边、尺寸偏差），拍清晰照片联系客服，我们核实后给您处理或补发。</t>
+          <t>亲，本店裁剪（也常写剪裁）质量您放心哦。每米面料出厂前都经过验布和质检，裁切边缘平整、不毛边、尺寸精准，多拍的件数会按订单规格米数连成整段一起裁。如果您收到的裁剪质量不满意（如毛边、尺寸偏差），拍清晰照片联系客服，我们核实后给您处理或补发。</t>
         </is>
       </c>
     </row>

--- a/customer_service_import_template_安全版.xlsx
+++ b/customer_service_import_template_安全版.xlsx
@@ -592,7 +592,7 @@
         <is>
           <t>亲，本店面料按商品规格售卖，规格上有的米数才能下单，规格没有的长度不卖。
 普通花型（幅宽1.41~1.45米）只售整米：1米、2米、3米……即规格的整米倍数。
-花型名称含「贡缎」且幅宽1.5米的花型，可售0.5米递增：2.5米、3.5米、4.5米等，但其他小数米（如1.2米、2.3米）仍不卖。
+贡缎类花型（花型名称含「贡缎」且幅宽1.5米）：支持0.5米递增，1.5米、2.5米、3.5米等，规格里有的都能下单。
 多拍连裁：您拍几件，我们就把该规格的长度连成整段一起裁切。例如规格是2米，您拍2件就是4米一整段。</t>
         </is>
       </c>
@@ -699,9 +699,9 @@
       <c r="D11" s="3" t="inlineStr">
         <is>
           <t>亲，本店面料不卖特殊尺寸，只按商品规格售卖。
-• 普通花型只售整米（1米、2米、3米及倍数），不卖1.5米、2.5米等小数米。
-• 只有花型名称含「贡缎」且幅宽1.5米的花型，才支持0.5米递增（如2.5米、3.5米），其他小数米同样不卖。
-• 规格里有1.5米就可以买1.5米；规格里没有的小数米，请按最接近的整米规格下单。</t>
+• 先看买家当前咨询的商品：花型名称含「贡缎」且幅宽1.5米 → 该商品支持0.5米递增，1.5米、2.5米、3.5米等规格里有的都能买，直接答复可以买。
+• 普通花型（幅宽1.41~1.45米）只售整米（1米、2米、3米及倍数），不卖小数米。
+• 无论哪种花型，0.5米递增以外的小数米（如1.2米、2.3米）都不卖；规格里没有的长度不卖。</t>
         </is>
       </c>
     </row>

--- a/customer_service_import_template_安全版.xlsx
+++ b/customer_service_import_template_安全版.xlsx
@@ -590,10 +590,10 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>亲，本店面料按商品规格售卖，规格上有的米数才能下单，规格没有的长度不卖。
-普通花型（幅宽1.41~1.45米）只售整米：1米、2米、3米……即规格的整米倍数。
-贡缎类花型（花型名称含「贡缎」且幅宽1.5米）：支持0.5米递增，1.5米、2.5米、3.5米等，规格里有的都能下单。
-多拍连裁：您拍几件，我们就把该规格的长度连成整段一起裁切。例如规格是2米，您拍2件就是4米一整段。</t>
+          <t>亲，本店面料按商品规格售卖，规格上有的米数才能下单。
+普通花型（幅宽1.41~1.45米）只售整米：1米、2米、3米及倍数，整米可以通过多拍组合实现。例如您要4米就拍2个2米，要5米就拍2米+3米各一件，要6米就拍2个3米或3个2米，我们都会连成整段一起裁切。
+贡缎类花型（花型名称含「贡缎」且幅宽1.5米）：支持0.5米递增，1.5米、2.5米、3.5米等规格里有的都能下单。
+不能卖的是：规格库里无法组合出来的长度、0.5米递增以外的小数米（如1.2米、2.3米）、以及任何要求备注/定制/按需裁剪的特殊长度。</t>
         </is>
       </c>
     </row>
@@ -700,8 +700,8 @@
         <is>
           <t>亲，本店面料不卖特殊尺寸，只按商品规格售卖。
 • 先看买家当前咨询的商品：花型名称含「贡缎」且幅宽1.5米 → 该商品支持0.5米递增，1.5米、2.5米、3.5米等规格里有的都能买，直接答复可以买。
-• 普通花型（幅宽1.41~1.45米）只售整米（1米、2米、3米及倍数），不卖小数米。
-• 无论哪种花型，0.5米递增以外的小数米（如1.2米、2.3米）都不卖；规格里没有的长度不卖。</t>
+• 普通花型（幅宽1.41~1.45米）只售整米：1米、2米、3米及倍数。整米可以通过多拍组合实现，例如4米拍2个2米、5米拍2米+3米、6米拍2个3米或3个2米。不要对整米需求说"不支持""面料长度固定"。
+• 不能卖的是：规格库里无法组合出来的长度、0.5米递增以外的小数米（如1.2米、2.3米）、以及任何要求备注/定制/按需裁剪的特殊长度。</t>
         </is>
       </c>
     </row>

--- a/customer_service_import_template_安全版.xlsx
+++ b/customer_service_import_template_安全版.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" style="4" min="1" max="2"/>
@@ -705,6 +705,28 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>物流</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>运费险</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>运费险</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>亲，本店商品不带运费险哦。面料是剪裁类商品，不支持无理由退换，所以也没有赠送运费险。如果是质量问题、错发或漏发，您拍清晰照片联系我们核实，运费由我们承担，会给您安排退换或补发，请放心。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
